--- a/606-22_ДемьянцевВВ_Лаб6.xlsx
+++ b/606-22_ДемьянцевВВ_Лаб6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vital\OneDrive\Рабочий стол\metrology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E3AB6E-3F80-4CFA-9A76-C7455E039690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742CC430-DCBF-46AC-AB10-5D0AD07FE3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1326,7 +1326,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1389,7 +1389,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1447,7 +1447,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="800"/>
       </a:pPr>
       <a:endParaRPr lang="ru-RU"/>
     </a:p>
@@ -2012,13 +2012,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>280145</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>81641</xdr:rowOff>
+      <xdr:rowOff>81640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>190499</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123265</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>582706</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
